--- a/corep_data.xlsx
+++ b/corep_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="8400" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="1" r:id="rId1"/>
@@ -964,7 +964,7 @@
 Highly hypertensive</t>
   </si>
   <si>
-    <t>HTN
+    <t>Hypertension
 Arthritis</t>
   </si>
   <si>
@@ -1031,9 +1031,6 @@
 Leg pains after walking</t>
   </si>
   <si>
-    <t>HTN</t>
-  </si>
-  <si>
     <t>Tab amlodipine 5mg dly x1/52
 Tab diclofenanc 50mg bid x57
 Tab calcium 300mg dly x2/52</t>
@@ -1042,7 +1039,7 @@
     <t>Pains</t>
   </si>
   <si>
-    <t>Pneumonia 
+    <t>Pneumonia
 Arthritis</t>
   </si>
   <si>
@@ -1117,7 +1114,7 @@
     <t>Ulcer patient</t>
   </si>
   <si>
-    <t>HTN
+    <t>Hypertension
 Ulcer</t>
   </si>
   <si>
@@ -1257,7 +1254,7 @@
 Feeling body hotness internally</t>
   </si>
   <si>
-    <t>PUD/HTN</t>
+    <t>Pelvic Ulcer Disease Hypertension</t>
   </si>
   <si>
     <t>Tab Amlodepine 5mg dlyx2/52
@@ -1463,6 +1460,10 @@
     <t>Shivering 
 Cattarh 
 Joint pains</t>
+  </si>
+  <si>
+    <t>Pneumonia 
+Arthritis</t>
   </si>
   <si>
     <t>Tab Cefixime 400mg dly x2/52
@@ -7404,9 +7405,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -7820,7 +7824,7 @@
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="3">
         <v>26353</v>
       </c>
       <c r="G2" t="s">
@@ -7855,7 +7859,7 @@
       <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>24532</v>
       </c>
       <c r="G3" t="s">
@@ -7890,7 +7894,7 @@
       <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>30310</v>
       </c>
       <c r="G4" t="s">
@@ -7925,7 +7929,7 @@
       <c r="E5" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>15897</v>
       </c>
       <c r="G5" t="s">
@@ -7960,7 +7964,7 @@
       <c r="E6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>19441</v>
       </c>
       <c r="G6" t="s">
@@ -7995,7 +7999,7 @@
       <c r="E7" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>27149</v>
       </c>
       <c r="G7" t="s">
@@ -8030,7 +8034,7 @@
       <c r="E8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="3">
         <v>25473</v>
       </c>
       <c r="G8" t="s">
@@ -8065,7 +8069,7 @@
       <c r="E9" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>16803</v>
       </c>
       <c r="G9" t="s">
@@ -8100,7 +8104,7 @@
       <c r="E10" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>34398</v>
       </c>
       <c r="G10" t="s">
@@ -8135,7 +8139,7 @@
       <c r="E11" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>23683</v>
       </c>
       <c r="G11" t="s">
@@ -8170,7 +8174,7 @@
       <c r="E12" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>34984</v>
       </c>
       <c r="G12" t="s">
@@ -8205,7 +8209,7 @@
       <c r="E13" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="3">
         <v>24466</v>
       </c>
       <c r="G13" t="s">
@@ -8240,7 +8244,7 @@
       <c r="E14" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
         <v>22362</v>
       </c>
       <c r="G14" t="s">
@@ -8275,7 +8279,7 @@
       <c r="E15" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <v>32020</v>
       </c>
       <c r="G15" t="s">
@@ -8310,7 +8314,7 @@
       <c r="E16" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="3">
         <v>23668</v>
       </c>
       <c r="G16" t="s">
@@ -8345,7 +8349,7 @@
       <c r="E17" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="3">
         <v>26816</v>
       </c>
       <c r="G17" t="s">
@@ -8380,7 +8384,7 @@
       <c r="E18" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="3">
         <v>20090</v>
       </c>
       <c r="G18" t="s">
@@ -8415,7 +8419,7 @@
       <c r="E19" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="3">
         <v>17714</v>
       </c>
       <c r="G19" t="s">
@@ -8450,7 +8454,7 @@
       <c r="E20" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="3">
         <v>20090</v>
       </c>
       <c r="G20" t="s">
@@ -8485,7 +8489,7 @@
       <c r="E21" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
         <v>19524</v>
       </c>
       <c r="G21" t="s">
@@ -8520,7 +8524,7 @@
       <c r="E22" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="3">
         <v>25569</v>
       </c>
       <c r="G22" t="s">
@@ -8555,7 +8559,7 @@
       <c r="E23" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="3">
         <v>23435</v>
       </c>
       <c r="G23" t="s">
@@ -8590,7 +8594,7 @@
       <c r="E24" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="3">
         <v>27733</v>
       </c>
       <c r="G24" t="s">
@@ -8625,7 +8629,7 @@
       <c r="E25" t="s">
         <v>11</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="3">
         <v>45857</v>
       </c>
       <c r="G25" t="s">
@@ -8660,7 +8664,7 @@
       <c r="E26" t="s">
         <v>11</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="3">
         <v>30480</v>
       </c>
       <c r="G26" t="s">
@@ -8695,7 +8699,7 @@
       <c r="E27" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="3">
         <v>28105</v>
       </c>
       <c r="G27" t="s">
@@ -8730,7 +8734,7 @@
       <c r="E28" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="3">
         <v>31674</v>
       </c>
       <c r="G28" t="s">
@@ -8765,7 +8769,7 @@
       <c r="E29" t="s">
         <v>11</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="3">
         <v>30834</v>
       </c>
       <c r="G29" t="s">
@@ -8800,7 +8804,7 @@
       <c r="E30" t="s">
         <v>11</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="3">
         <v>18247</v>
       </c>
       <c r="G30" t="s">
@@ -8835,7 +8839,7 @@
       <c r="E31" t="s">
         <v>11</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>29973</v>
       </c>
       <c r="G31" t="s">
@@ -8870,7 +8874,7 @@
       <c r="E32" t="s">
         <v>11</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="3">
         <v>30731</v>
       </c>
       <c r="G32" t="s">
@@ -8905,7 +8909,7 @@
       <c r="E33" t="s">
         <v>11</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="3">
         <v>45057</v>
       </c>
       <c r="G33" t="s">
@@ -8940,7 +8944,7 @@
       <c r="E34" t="s">
         <v>11</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="3">
         <v>28537</v>
       </c>
       <c r="G34" t="s">
@@ -8975,7 +8979,7 @@
       <c r="E35" t="s">
         <v>11</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="3">
         <v>35658</v>
       </c>
       <c r="G35" t="s">
@@ -9010,7 +9014,7 @@
       <c r="E36" t="s">
         <v>11</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="3">
         <v>21520</v>
       </c>
       <c r="G36" t="s">
@@ -9045,7 +9049,7 @@
       <c r="E37" t="s">
         <v>11</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="3">
         <v>44732</v>
       </c>
       <c r="G37" t="s">
@@ -9080,7 +9084,7 @@
       <c r="E38" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="3">
         <v>27317</v>
       </c>
       <c r="G38" t="s">
@@ -9115,7 +9119,7 @@
       <c r="E39" t="s">
         <v>11</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="3">
         <v>45577</v>
       </c>
       <c r="G39" t="s">
@@ -9150,7 +9154,7 @@
       <c r="E40" t="s">
         <v>11</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="3">
         <v>36161</v>
       </c>
       <c r="G40" t="s">
@@ -9185,7 +9189,7 @@
       <c r="E41">
         <v>1</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="3">
         <v>36408</v>
       </c>
       <c r="G41" t="s">
@@ -9220,7 +9224,7 @@
       <c r="E42" t="s">
         <v>11</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="3">
         <v>39313</v>
       </c>
       <c r="G42" t="s">
@@ -9255,7 +9259,7 @@
       <c r="E43" t="s">
         <v>11</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="3">
         <v>22647</v>
       </c>
       <c r="G43" t="s">
@@ -9290,7 +9294,7 @@
       <c r="E44" t="s">
         <v>11</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="3">
         <v>29615</v>
       </c>
       <c r="G44" t="s">
@@ -9325,7 +9329,7 @@
       <c r="E45" t="s">
         <v>11</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="3">
         <v>26948</v>
       </c>
       <c r="G45" t="s">
@@ -9360,7 +9364,7 @@
       <c r="E46" t="s">
         <v>11</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="3">
         <v>22192</v>
       </c>
       <c r="G46" t="s">
@@ -9395,7 +9399,7 @@
       <c r="E47" t="s">
         <v>11</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="3">
         <v>19725</v>
       </c>
       <c r="G47" t="s">
@@ -9430,7 +9434,7 @@
       <c r="E48" t="s">
         <v>11</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="3">
         <v>26758</v>
       </c>
       <c r="G48" t="s">
@@ -9465,7 +9469,7 @@
       <c r="E49" t="s">
         <v>11</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="3">
         <v>16072</v>
       </c>
       <c r="G49" t="s">
@@ -9500,7 +9504,7 @@
       <c r="E50" t="s">
         <v>11</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="3">
         <v>29587</v>
       </c>
       <c r="G50" t="s">
@@ -9535,7 +9539,7 @@
       <c r="E51" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="3">
         <v>26411</v>
       </c>
       <c r="G51" t="s">
@@ -9570,7 +9574,7 @@
       <c r="E52" t="s">
         <v>11</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="3">
         <v>27371</v>
       </c>
       <c r="G52" t="s">
@@ -9605,7 +9609,7 @@
       <c r="E53" t="s">
         <v>11</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="3">
         <v>27529</v>
       </c>
       <c r="G53" t="s">
@@ -9640,7 +9644,7 @@
       <c r="E54" t="s">
         <v>11</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="3">
         <v>38455</v>
       </c>
       <c r="G54" t="s">
@@ -9675,7 +9679,7 @@
       <c r="E55" t="s">
         <v>11</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="3">
         <v>45165</v>
       </c>
       <c r="G55" t="s">
@@ -9710,7 +9714,7 @@
       <c r="E56" t="s">
         <v>11</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="3">
         <v>24692</v>
       </c>
       <c r="G56" t="s">
@@ -9745,7 +9749,7 @@
       <c r="E57" t="s">
         <v>11</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="3">
         <v>22190</v>
       </c>
       <c r="G57" t="s">
@@ -9780,7 +9784,7 @@
       <c r="E58" t="s">
         <v>11</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="3">
         <v>37950</v>
       </c>
       <c r="G58" t="s">
@@ -9815,7 +9819,7 @@
       <c r="E59" t="s">
         <v>11</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="3">
         <v>22079</v>
       </c>
       <c r="G59" t="s">
@@ -9850,7 +9854,7 @@
       <c r="E60" t="s">
         <v>11</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="3">
         <v>32603</v>
       </c>
       <c r="G60" t="s">
@@ -9885,7 +9889,7 @@
       <c r="E61" t="s">
         <v>11</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="3">
         <v>24373</v>
       </c>
       <c r="G61" t="s">
@@ -9920,7 +9924,7 @@
       <c r="E62" t="s">
         <v>11</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="3">
         <v>30066</v>
       </c>
       <c r="G62" t="s">
@@ -9955,7 +9959,7 @@
       <c r="E63" t="s">
         <v>11</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="3">
         <v>29158</v>
       </c>
       <c r="G63" t="s">
@@ -9990,7 +9994,7 @@
       <c r="E64" t="s">
         <v>11</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="3">
         <v>27321</v>
       </c>
       <c r="G64" t="s">
@@ -10025,7 +10029,7 @@
       <c r="E65" t="s">
         <v>11</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="3">
         <v>27447</v>
       </c>
       <c r="G65" t="s">
@@ -10060,7 +10064,7 @@
       <c r="E66" t="s">
         <v>11</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="3">
         <v>40807</v>
       </c>
       <c r="G66" t="s">
@@ -10095,7 +10099,7 @@
       <c r="E67" t="s">
         <v>11</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="3">
         <v>26573</v>
       </c>
       <c r="G67" t="s">
@@ -10130,7 +10134,7 @@
       <c r="E68" t="s">
         <v>11</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="3">
         <v>33025</v>
       </c>
       <c r="G68" t="s">
@@ -10165,7 +10169,7 @@
       <c r="E69" t="s">
         <v>11</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="3">
         <v>26122</v>
       </c>
       <c r="G69" t="s">
@@ -10200,7 +10204,7 @@
       <c r="E70" t="s">
         <v>11</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="3">
         <v>35109</v>
       </c>
       <c r="G70" t="s">
@@ -10235,7 +10239,7 @@
       <c r="E71" t="s">
         <v>11</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="3">
         <v>44678</v>
       </c>
       <c r="G71" t="s">
@@ -10270,7 +10274,7 @@
       <c r="E72" t="s">
         <v>11</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="3">
         <v>44119</v>
       </c>
       <c r="G72" t="s">
@@ -10305,7 +10309,7 @@
       <c r="E73" t="s">
         <v>11</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="3">
         <v>45943</v>
       </c>
       <c r="G73" t="s">
@@ -10340,7 +10344,7 @@
       <c r="E74" t="s">
         <v>11</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="3">
         <v>46129</v>
       </c>
       <c r="G74" t="s">
@@ -10375,7 +10379,7 @@
       <c r="E75" t="s">
         <v>11</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="3">
         <v>36800</v>
       </c>
       <c r="G75" t="s">
@@ -10410,7 +10414,7 @@
       <c r="E76" t="s">
         <v>11</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="3">
         <v>27754</v>
       </c>
       <c r="G76" t="s">
@@ -10445,7 +10449,7 @@
       <c r="E77" t="s">
         <v>11</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="3">
         <v>46158</v>
       </c>
       <c r="G77" t="s">
@@ -10480,7 +10484,7 @@
       <c r="E78" t="s">
         <v>11</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="3">
         <v>26738</v>
       </c>
       <c r="G78" t="s">
@@ -10515,7 +10519,7 @@
       <c r="E79" t="s">
         <v>11</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="3">
         <v>36132</v>
       </c>
       <c r="G79" t="s">
@@ -10550,7 +10554,7 @@
       <c r="E80" t="s">
         <v>11</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="3">
         <v>30538</v>
       </c>
       <c r="G80" t="s">
@@ -10585,7 +10589,7 @@
       <c r="E81" t="s">
         <v>11</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="3">
         <v>43501</v>
       </c>
       <c r="G81" t="s">
@@ -10620,7 +10624,7 @@
       <c r="E82" t="s">
         <v>11</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="3">
         <v>29383</v>
       </c>
       <c r="G82" t="s">
@@ -10655,7 +10659,7 @@
       <c r="E83" t="s">
         <v>11</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="3">
         <v>33857</v>
       </c>
       <c r="G83" t="s">
@@ -10690,7 +10694,7 @@
       <c r="E84" t="s">
         <v>11</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="3">
         <v>25833</v>
       </c>
       <c r="G84" t="s">
@@ -10725,7 +10729,7 @@
       <c r="E85" t="s">
         <v>11</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="3">
         <v>27192</v>
       </c>
       <c r="G85" t="s">
@@ -10760,7 +10764,7 @@
       <c r="E86" t="s">
         <v>11</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="3">
         <v>20764</v>
       </c>
       <c r="G86" t="s">
@@ -10795,7 +10799,7 @@
       <c r="E87" t="s">
         <v>11</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="3">
         <v>27107</v>
       </c>
       <c r="G87" t="s">
@@ -10830,7 +10834,7 @@
       <c r="E88" t="s">
         <v>11</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="3">
         <v>39179</v>
       </c>
       <c r="G88" t="s">
@@ -10865,7 +10869,7 @@
       <c r="E89" t="s">
         <v>11</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="3">
         <v>39533</v>
       </c>
       <c r="G89" t="s">
@@ -10900,7 +10904,7 @@
       <c r="E90" t="s">
         <v>11</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="3">
         <v>24116</v>
       </c>
       <c r="G90" t="s">
@@ -10935,7 +10939,7 @@
       <c r="E91" t="s">
         <v>11</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="3">
         <v>31040</v>
       </c>
       <c r="G91" t="s">
@@ -10970,7 +10974,7 @@
       <c r="E92" t="s">
         <v>11</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="3">
         <v>25916</v>
       </c>
       <c r="G92" t="s">
@@ -11005,7 +11009,7 @@
       <c r="E93" t="s">
         <v>11</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="3">
         <v>23377</v>
       </c>
       <c r="G93" t="s">
@@ -11040,7 +11044,7 @@
       <c r="E94" t="s">
         <v>11</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="3">
         <v>20090</v>
       </c>
       <c r="G94" t="s">
@@ -11075,7 +11079,7 @@
       <c r="E95" t="s">
         <v>11</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="3">
         <v>20809</v>
       </c>
       <c r="G95" t="s">
@@ -11110,7 +11114,7 @@
       <c r="E96" t="s">
         <v>11</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="3">
         <v>29875</v>
       </c>
       <c r="G96" t="s">
@@ -11145,7 +11149,7 @@
       <c r="E97" t="s">
         <v>11</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="3">
         <v>18264</v>
       </c>
       <c r="G97" t="s">
@@ -11180,7 +11184,7 @@
       <c r="E98" t="s">
         <v>11</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="3">
         <v>26299</v>
       </c>
       <c r="G98" t="s">
@@ -11215,7 +11219,7 @@
       <c r="E99" t="s">
         <v>11</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="3">
         <v>26534</v>
       </c>
       <c r="G99" t="s">
@@ -11250,7 +11254,7 @@
       <c r="E100" t="s">
         <v>11</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="3">
         <v>41192</v>
       </c>
       <c r="G100" t="s">
@@ -11285,7 +11289,7 @@
       <c r="E101" t="s">
         <v>11</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F101" s="3">
         <v>25357</v>
       </c>
       <c r="G101" t="s">
@@ -11320,7 +11324,7 @@
       <c r="E102" t="s">
         <v>11</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="3">
         <v>39731</v>
       </c>
       <c r="G102" t="s">
@@ -11355,7 +11359,7 @@
       <c r="E103" t="s">
         <v>11</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="3">
         <v>21916</v>
       </c>
       <c r="G103" t="s">
@@ -11390,7 +11394,7 @@
       <c r="E104" t="s">
         <v>11</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="3">
         <v>20821</v>
       </c>
       <c r="G104" t="s">
@@ -11425,7 +11429,7 @@
       <c r="E105" t="s">
         <v>11</v>
       </c>
-      <c r="F105" s="2">
+      <c r="F105" s="3">
         <v>28896</v>
       </c>
       <c r="G105" t="s">
@@ -11460,7 +11464,7 @@
       <c r="E106" t="s">
         <v>11</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="3">
         <v>43001</v>
       </c>
       <c r="G106" t="s">
@@ -11495,7 +11499,7 @@
       <c r="E107" t="s">
         <v>11</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="3">
         <v>25194</v>
       </c>
       <c r="G107" t="s">
@@ -11530,7 +11534,7 @@
       <c r="E108" t="s">
         <v>11</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="3">
         <v>44199</v>
       </c>
       <c r="G108" t="s">
@@ -11565,7 +11569,7 @@
       <c r="E109" t="s">
         <v>11</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="3">
         <v>41336</v>
       </c>
       <c r="G109" t="s">
@@ -11600,7 +11604,7 @@
       <c r="E110" t="s">
         <v>11</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="3">
         <v>19341</v>
       </c>
       <c r="G110" t="s">
@@ -11635,7 +11639,7 @@
       <c r="E111" t="s">
         <v>11</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="3">
         <v>41216</v>
       </c>
       <c r="G111" t="s">
@@ -11670,7 +11674,7 @@
       <c r="E112" t="s">
         <v>11</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="3">
         <v>40811</v>
       </c>
       <c r="G112" t="s">
@@ -11705,7 +11709,7 @@
       <c r="E113" t="s">
         <v>11</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="3">
         <v>17533</v>
       </c>
       <c r="G113" t="s">
@@ -11740,7 +11744,7 @@
       <c r="E114" t="s">
         <v>11</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="3">
         <v>22082</v>
       </c>
       <c r="G114" t="s">
@@ -11775,7 +11779,7 @@
       <c r="E115" t="s">
         <v>11</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="3">
         <v>41152</v>
       </c>
       <c r="G115" t="s">
@@ -11810,7 +11814,7 @@
       <c r="E116" t="s">
         <v>11</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="3">
         <v>41795</v>
       </c>
       <c r="G116" t="s">
@@ -11845,7 +11849,7 @@
       <c r="E117" t="s">
         <v>11</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="3">
         <v>18994</v>
       </c>
       <c r="G117" t="s">
@@ -11880,7 +11884,7 @@
       <c r="E118" t="s">
         <v>11</v>
       </c>
-      <c r="F118" s="2">
+      <c r="F118" s="3">
         <v>45538</v>
       </c>
       <c r="G118" t="s">
@@ -11915,7 +11919,7 @@
       <c r="E119" t="s">
         <v>11</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="3">
         <v>21398</v>
       </c>
       <c r="G119" t="s">
@@ -11950,7 +11954,7 @@
       <c r="E120" t="s">
         <v>11</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="3">
         <v>43339</v>
       </c>
       <c r="G120" t="s">
@@ -11985,7 +11989,7 @@
       <c r="E121" t="s">
         <v>11</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="3">
         <v>39945</v>
       </c>
       <c r="G121" t="s">
@@ -12020,7 +12024,7 @@
       <c r="E122" t="s">
         <v>11</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="3">
         <v>27476</v>
       </c>
       <c r="G122" t="s">
@@ -12055,7 +12059,7 @@
       <c r="E123" t="s">
         <v>11</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="3">
         <v>41723</v>
       </c>
       <c r="G123" t="s">
@@ -12090,7 +12094,7 @@
       <c r="E124" t="s">
         <v>11</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="3">
         <v>40530</v>
       </c>
       <c r="G124" t="s">
@@ -12125,7 +12129,7 @@
       <c r="E125" t="s">
         <v>11</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="3">
         <v>21551</v>
       </c>
       <c r="G125" t="s">
@@ -12160,7 +12164,7 @@
       <c r="E126" t="s">
         <v>11</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="3">
         <v>25674</v>
       </c>
       <c r="G126" t="s">
@@ -12195,7 +12199,7 @@
       <c r="E127" t="s">
         <v>11</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="3">
         <v>26101</v>
       </c>
       <c r="G127" t="s">
@@ -12230,7 +12234,7 @@
       <c r="E128" t="s">
         <v>11</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="3">
         <v>25569</v>
       </c>
       <c r="G128" t="s">
@@ -12265,7 +12269,7 @@
       <c r="E129" t="s">
         <v>11</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="3">
         <v>20675</v>
       </c>
       <c r="G129" t="s">
@@ -12300,7 +12304,7 @@
       <c r="E130" t="s">
         <v>11</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="3">
         <v>18629</v>
       </c>
       <c r="G130" t="s">
@@ -12335,7 +12339,7 @@
       <c r="E131" t="s">
         <v>11</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="3">
         <v>23743</v>
       </c>
       <c r="G131" t="s">
@@ -12370,7 +12374,7 @@
       <c r="E132" t="s">
         <v>11</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="3">
         <v>23048</v>
       </c>
       <c r="G132" t="s">
@@ -12405,7 +12409,7 @@
       <c r="E133" t="s">
         <v>11</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="3">
         <v>30947</v>
       </c>
       <c r="G133" t="s">
@@ -12440,7 +12444,7 @@
       <c r="E134" t="s">
         <v>11</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="3">
         <v>30398</v>
       </c>
       <c r="G134" t="s">
@@ -12475,7 +12479,7 @@
       <c r="E135" t="s">
         <v>11</v>
       </c>
-      <c r="F135" s="2">
+      <c r="F135" s="3">
         <v>20455</v>
       </c>
       <c r="G135" t="s">
@@ -12510,7 +12514,7 @@
       <c r="E136" t="s">
         <v>11</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="3">
         <v>18809</v>
       </c>
       <c r="G136" t="s">
@@ -12545,7 +12549,7 @@
       <c r="E137" t="s">
         <v>11</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="3">
         <v>37517</v>
       </c>
       <c r="G137" t="s">
@@ -12580,7 +12584,7 @@
       <c r="E138" t="s">
         <v>11</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="3">
         <v>38518</v>
       </c>
       <c r="G138" t="s">
@@ -12615,7 +12619,7 @@
       <c r="E139" t="s">
         <v>11</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="3">
         <v>33419</v>
       </c>
       <c r="G139" t="s">
@@ -12650,7 +12654,7 @@
       <c r="E140" t="s">
         <v>11</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="3">
         <v>25066</v>
       </c>
       <c r="G140" t="s">
@@ -12685,7 +12689,7 @@
       <c r="E141" t="s">
         <v>11</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="3">
         <v>26660</v>
       </c>
       <c r="G141" t="s">
@@ -12720,7 +12724,7 @@
       <c r="E142" t="s">
         <v>11</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="3">
         <v>31274</v>
       </c>
       <c r="G142" t="s">
@@ -12755,7 +12759,7 @@
       <c r="E143" t="s">
         <v>11</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="3">
         <v>40828</v>
       </c>
       <c r="G143" t="s">
@@ -12790,7 +12794,7 @@
       <c r="E144" t="s">
         <v>11</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="3">
         <v>41113</v>
       </c>
       <c r="G144" t="s">
@@ -12825,7 +12829,7 @@
       <c r="E145" t="s">
         <v>11</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="3">
         <v>43792</v>
       </c>
       <c r="G145" t="s">
@@ -12860,7 +12864,7 @@
       <c r="E146" t="s">
         <v>11</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="3">
         <v>24008</v>
       </c>
       <c r="G146" t="s">
@@ -12895,7 +12899,7 @@
       <c r="E147" t="s">
         <v>11</v>
       </c>
-      <c r="F147" s="2">
+      <c r="F147" s="3">
         <v>41846</v>
       </c>
       <c r="G147" t="s">
@@ -12930,7 +12934,7 @@
       <c r="E148" t="s">
         <v>11</v>
       </c>
-      <c r="F148" s="2">
+      <c r="F148" s="3">
         <v>38915</v>
       </c>
       <c r="G148" t="s">
@@ -12965,7 +12969,7 @@
       <c r="E149" t="s">
         <v>11</v>
       </c>
-      <c r="F149" s="2">
+      <c r="F149" s="3">
         <v>27053</v>
       </c>
       <c r="G149" t="s">
@@ -13000,7 +13004,7 @@
       <c r="E150" t="s">
         <v>11</v>
       </c>
-      <c r="F150" s="2">
+      <c r="F150" s="3">
         <v>26778</v>
       </c>
       <c r="G150" t="s">
@@ -13035,7 +13039,7 @@
       <c r="E151" t="s">
         <v>11</v>
       </c>
-      <c r="F151" s="2">
+      <c r="F151" s="3">
         <v>17899</v>
       </c>
       <c r="G151" t="s">
@@ -13070,7 +13074,7 @@
       <c r="E152" t="s">
         <v>11</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="3">
         <v>26552</v>
       </c>
       <c r="G152" t="s">
@@ -13105,7 +13109,7 @@
       <c r="E153" t="s">
         <v>11</v>
       </c>
-      <c r="F153" s="2">
+      <c r="F153" s="3">
         <v>24294</v>
       </c>
       <c r="G153" t="s">
@@ -13140,7 +13144,7 @@
       <c r="E154" t="s">
         <v>11</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="3">
         <v>43466</v>
       </c>
       <c r="G154" t="s">
@@ -13175,7 +13179,7 @@
       <c r="E155" t="s">
         <v>11</v>
       </c>
-      <c r="F155" s="2">
+      <c r="F155" s="3">
         <v>26269</v>
       </c>
       <c r="G155" t="s">
@@ -13210,7 +13214,7 @@
       <c r="E156" t="s">
         <v>11</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="3">
         <v>26547</v>
       </c>
       <c r="G156" t="s">
@@ -13245,7 +13249,7 @@
       <c r="E157" t="s">
         <v>11</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="3">
         <v>43337</v>
       </c>
       <c r="G157" t="s">
@@ -13280,7 +13284,7 @@
       <c r="E158" t="s">
         <v>11</v>
       </c>
-      <c r="F158" s="2">
+      <c r="F158" s="3">
         <v>20465</v>
       </c>
       <c r="G158" t="s">
@@ -13315,7 +13319,7 @@
       <c r="E159" t="s">
         <v>11</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="3">
         <v>42727</v>
       </c>
       <c r="G159" t="s">
@@ -13350,7 +13354,7 @@
       <c r="E160" t="s">
         <v>11</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="3">
         <v>43318</v>
       </c>
       <c r="G160" t="s">
@@ -13385,7 +13389,7 @@
       <c r="E161" t="s">
         <v>11</v>
       </c>
-      <c r="F161" s="2">
+      <c r="F161" s="3">
         <v>22073</v>
       </c>
       <c r="G161" t="s">
@@ -13420,7 +13424,7 @@
       <c r="E162" t="s">
         <v>11</v>
       </c>
-      <c r="F162" s="2">
+      <c r="F162" s="3">
         <v>44197</v>
       </c>
       <c r="G162" t="s">
@@ -13455,7 +13459,7 @@
       <c r="E163" t="s">
         <v>11</v>
       </c>
-      <c r="F163" s="2">
+      <c r="F163" s="3">
         <v>24288</v>
       </c>
       <c r="G163" t="s">
@@ -13490,7 +13494,7 @@
       <c r="E164" t="s">
         <v>11</v>
       </c>
-      <c r="F164" s="2">
+      <c r="F164" s="3">
         <v>37501</v>
       </c>
       <c r="G164" t="s">
@@ -13525,7 +13529,7 @@
       <c r="E165" t="s">
         <v>11</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="3">
         <v>23192</v>
       </c>
       <c r="G165" t="s">
@@ -13560,7 +13564,7 @@
       <c r="E166" t="s">
         <v>11</v>
       </c>
-      <c r="F166" s="2">
+      <c r="F166" s="3">
         <v>44666</v>
       </c>
       <c r="G166" t="s">
@@ -13595,7 +13599,7 @@
       <c r="E167" t="s">
         <v>11</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="3">
         <v>36037</v>
       </c>
       <c r="G167" t="s">
@@ -13630,7 +13634,7 @@
       <c r="E168" t="s">
         <v>11</v>
       </c>
-      <c r="F168" s="2">
+      <c r="F168" s="3">
         <v>44984</v>
       </c>
       <c r="G168" t="s">
@@ -13665,7 +13669,7 @@
       <c r="E169" t="s">
         <v>11</v>
       </c>
-      <c r="F169" s="2">
+      <c r="F169" s="3">
         <v>42032</v>
       </c>
       <c r="G169" t="s">
@@ -13700,7 +13704,7 @@
       <c r="E170" t="s">
         <v>11</v>
       </c>
-      <c r="F170" s="2">
+      <c r="F170" s="3">
         <v>46152</v>
       </c>
       <c r="G170" t="s">
@@ -13735,7 +13739,7 @@
       <c r="E171" t="s">
         <v>11</v>
       </c>
-      <c r="F171" s="2">
+      <c r="F171" s="3">
         <v>44357</v>
       </c>
       <c r="G171" t="s">
@@ -13770,7 +13774,7 @@
       <c r="E172" t="s">
         <v>11</v>
       </c>
-      <c r="F172" s="2">
+      <c r="F172" s="3">
         <v>44037</v>
       </c>
       <c r="G172" t="s">
@@ -13805,7 +13809,7 @@
       <c r="E173" t="s">
         <v>11</v>
       </c>
-      <c r="F173" s="2">
+      <c r="F173" s="3">
         <v>46151</v>
       </c>
       <c r="G173" t="s">
@@ -13840,7 +13844,7 @@
       <c r="E174" t="s">
         <v>11</v>
       </c>
-      <c r="F174" s="2">
+      <c r="F174" s="3">
         <v>44623</v>
       </c>
       <c r="G174" t="s">
@@ -13875,7 +13879,7 @@
       <c r="E175" t="s">
         <v>11</v>
       </c>
-      <c r="F175" s="2">
+      <c r="F175" s="3">
         <v>42184</v>
       </c>
       <c r="G175" t="s">
@@ -13910,7 +13914,7 @@
       <c r="E176" t="s">
         <v>11</v>
       </c>
-      <c r="F176" s="2">
+      <c r="F176" s="3">
         <v>42832</v>
       </c>
       <c r="G176" t="s">
@@ -13945,7 +13949,7 @@
       <c r="E177" t="s">
         <v>11</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F177" s="3">
         <v>25055</v>
       </c>
       <c r="G177" t="s">
@@ -13980,7 +13984,7 @@
       <c r="E178" t="s">
         <v>11</v>
       </c>
-      <c r="F178" s="2">
+      <c r="F178" s="3">
         <v>39990</v>
       </c>
       <c r="G178" t="s">
@@ -14015,7 +14019,7 @@
       <c r="E179" t="s">
         <v>11</v>
       </c>
-      <c r="F179" s="2">
+      <c r="F179" s="3">
         <v>42130</v>
       </c>
       <c r="G179" t="s">
@@ -14050,7 +14054,7 @@
       <c r="E180" t="s">
         <v>11</v>
       </c>
-      <c r="F180" s="2">
+      <c r="F180" s="3">
         <v>45063</v>
       </c>
       <c r="G180" t="s">
@@ -14085,7 +14089,7 @@
       <c r="E181" t="s">
         <v>11</v>
       </c>
-      <c r="F181" s="2">
+      <c r="F181" s="3">
         <v>42289</v>
       </c>
       <c r="G181" t="s">
@@ -14120,7 +14124,7 @@
       <c r="E182" t="s">
         <v>11</v>
       </c>
-      <c r="F182" s="2">
+      <c r="F182" s="3">
         <v>44012</v>
       </c>
       <c r="G182" t="s">
@@ -14155,7 +14159,7 @@
       <c r="E183" t="s">
         <v>11</v>
       </c>
-      <c r="F183" s="2">
+      <c r="F183" s="3">
         <v>25984</v>
       </c>
       <c r="G183" t="s">
@@ -14190,7 +14194,7 @@
       <c r="E184" t="s">
         <v>11</v>
       </c>
-      <c r="F184" s="2">
+      <c r="F184" s="3">
         <v>31146</v>
       </c>
       <c r="G184" t="s">
@@ -14225,7 +14229,7 @@
       <c r="E185" t="s">
         <v>11</v>
       </c>
-      <c r="F185" s="2">
+      <c r="F185" s="3">
         <v>36680</v>
       </c>
       <c r="G185" t="s">
@@ -14260,7 +14264,7 @@
       <c r="E186" t="s">
         <v>11</v>
       </c>
-      <c r="F186" s="2">
+      <c r="F186" s="3">
         <v>45532</v>
       </c>
       <c r="G186" t="s">
@@ -14295,7 +14299,7 @@
       <c r="E187" t="s">
         <v>11</v>
       </c>
-      <c r="F187" s="2">
+      <c r="F187" s="3">
         <v>43717</v>
       </c>
       <c r="G187" t="s">
@@ -14330,7 +14334,7 @@
       <c r="E188" t="s">
         <v>11</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="3">
         <v>41929</v>
       </c>
       <c r="G188" t="s">
@@ -14365,7 +14369,7 @@
       <c r="E189" t="s">
         <v>11</v>
       </c>
-      <c r="F189" s="2">
+      <c r="F189" s="3">
         <v>42427</v>
       </c>
       <c r="G189" t="s">
@@ -14400,7 +14404,7 @@
       <c r="E190" t="s">
         <v>11</v>
       </c>
-      <c r="F190" s="2">
+      <c r="F190" s="3">
         <v>29325</v>
       </c>
       <c r="G190" t="s">
@@ -28055,7 +28059,7 @@
         <v>46261.5819931012</v>
       </c>
     </row>
-    <row r="70" spans="1:17">
+    <row r="70" ht="28.8" spans="1:17">
       <c r="A70">
         <v>69</v>
       </c>
@@ -28080,7 +28084,7 @@
       <c r="H70" t="s">
         <v>210</v>
       </c>
-      <c r="I70" t="s">
+      <c r="I70" s="2" t="s">
         <v>211</v>
       </c>
       <c r="J70" t="s">
@@ -28452,10 +28456,10 @@
         <v>226</v>
       </c>
       <c r="I77" t="s">
+        <v>47</v>
+      </c>
+      <c r="J77" t="s">
         <v>227</v>
-      </c>
-      <c r="J77" t="s">
-        <v>228</v>
       </c>
       <c r="K77" t="s">
         <v>11</v>
@@ -28479,7 +28483,7 @@
         <v>46261.6084809669</v>
       </c>
     </row>
-    <row r="78" spans="1:17">
+    <row r="78" ht="28.8" spans="1:17">
       <c r="A78">
         <v>77</v>
       </c>
@@ -28502,13 +28506,13 @@
         <v>135</v>
       </c>
       <c r="H78" t="s">
+        <v>228</v>
+      </c>
+      <c r="I78" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="I78" t="s">
+      <c r="J78" t="s">
         <v>230</v>
-      </c>
-      <c r="J78" t="s">
-        <v>231</v>
       </c>
       <c r="K78" t="s">
         <v>11</v>
@@ -28558,10 +28562,10 @@
         <v>33</v>
       </c>
       <c r="I79" t="s">
+        <v>231</v>
+      </c>
+      <c r="J79" t="s">
         <v>232</v>
-      </c>
-      <c r="J79" t="s">
-        <v>233</v>
       </c>
       <c r="K79" t="s">
         <v>11</v>
@@ -28608,13 +28612,13 @@
         <v>74</v>
       </c>
       <c r="H80" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I80" t="s">
         <v>72</v>
       </c>
       <c r="J80" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K80" t="s">
         <v>11</v>
@@ -28661,13 +28665,13 @@
         <v>85</v>
       </c>
       <c r="H81" t="s">
+        <v>235</v>
+      </c>
+      <c r="I81" t="s">
         <v>236</v>
       </c>
-      <c r="I81" t="s">
+      <c r="J81" t="s">
         <v>237</v>
-      </c>
-      <c r="J81" t="s">
-        <v>238</v>
       </c>
       <c r="K81" t="s">
         <v>11</v>
@@ -28714,13 +28718,13 @@
         <v>71</v>
       </c>
       <c r="H82" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I82" t="s">
         <v>138</v>
       </c>
       <c r="J82" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K82" t="s">
         <v>11</v>
@@ -28767,13 +28771,13 @@
         <v>93</v>
       </c>
       <c r="H83" t="s">
+        <v>240</v>
+      </c>
+      <c r="I83" t="s">
         <v>241</v>
       </c>
-      <c r="I83" t="s">
+      <c r="J83" t="s">
         <v>242</v>
-      </c>
-      <c r="J83" t="s">
-        <v>243</v>
       </c>
       <c r="K83" t="s">
         <v>11</v>
@@ -28823,10 +28827,10 @@
         <v>33</v>
       </c>
       <c r="I84" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J84" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K84" t="s">
         <v>11</v>
@@ -28879,7 +28883,7 @@
         <v>67</v>
       </c>
       <c r="J85" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K85" t="s">
         <v>11</v>
@@ -28903,7 +28907,7 @@
         <v>46261.6303275016</v>
       </c>
     </row>
-    <row r="86" spans="1:17">
+    <row r="86" ht="28.8" spans="1:17">
       <c r="A86">
         <v>85</v>
       </c>
@@ -28926,13 +28930,13 @@
         <v>104</v>
       </c>
       <c r="H86" t="s">
+        <v>245</v>
+      </c>
+      <c r="I86" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="I86" t="s">
+      <c r="J86" t="s">
         <v>247</v>
-      </c>
-      <c r="J86" t="s">
-        <v>248</v>
       </c>
       <c r="K86" t="s">
         <v>11</v>
@@ -28979,13 +28983,13 @@
         <v>90</v>
       </c>
       <c r="H87" t="s">
+        <v>248</v>
+      </c>
+      <c r="I87" t="s">
         <v>249</v>
       </c>
-      <c r="I87" t="s">
+      <c r="J87" t="s">
         <v>250</v>
-      </c>
-      <c r="J87" t="s">
-        <v>251</v>
       </c>
       <c r="K87" t="s">
         <v>11</v>
@@ -29032,13 +29036,13 @@
         <v>87</v>
       </c>
       <c r="H88" t="s">
+        <v>251</v>
+      </c>
+      <c r="I88" t="s">
         <v>252</v>
       </c>
-      <c r="I88" t="s">
+      <c r="J88" t="s">
         <v>253</v>
-      </c>
-      <c r="J88" t="s">
-        <v>254</v>
       </c>
       <c r="K88" t="s">
         <v>11</v>
@@ -29085,13 +29089,13 @@
         <v>121</v>
       </c>
       <c r="H89" t="s">
+        <v>254</v>
+      </c>
+      <c r="I89" t="s">
         <v>255</v>
       </c>
-      <c r="I89" t="s">
+      <c r="J89" t="s">
         <v>256</v>
-      </c>
-      <c r="J89" t="s">
-        <v>257</v>
       </c>
       <c r="K89" t="s">
         <v>11</v>
@@ -29138,13 +29142,13 @@
         <v>134</v>
       </c>
       <c r="H90" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I90" t="s">
         <v>114</v>
       </c>
       <c r="J90" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K90" t="s">
         <v>11</v>
@@ -29191,13 +29195,13 @@
         <v>117</v>
       </c>
       <c r="H91" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I91" t="s">
         <v>114</v>
       </c>
       <c r="J91" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K91" t="s">
         <v>11</v>
@@ -29244,13 +29248,13 @@
         <v>84</v>
       </c>
       <c r="H92" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I92" t="s">
         <v>114</v>
       </c>
       <c r="J92" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K92" t="s">
         <v>11</v>
@@ -29297,13 +29301,13 @@
         <v>82</v>
       </c>
       <c r="H93" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I93" t="s">
         <v>67</v>
       </c>
       <c r="J93" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K93" t="s">
         <v>11</v>
@@ -29350,13 +29354,13 @@
         <v>136</v>
       </c>
       <c r="H94" t="s">
+        <v>265</v>
+      </c>
+      <c r="I94" t="s">
         <v>266</v>
       </c>
-      <c r="I94" t="s">
+      <c r="J94" t="s">
         <v>267</v>
-      </c>
-      <c r="J94" t="s">
-        <v>268</v>
       </c>
       <c r="K94" t="s">
         <v>11</v>
@@ -29403,13 +29407,13 @@
         <v>138</v>
       </c>
       <c r="H95" t="s">
+        <v>268</v>
+      </c>
+      <c r="I95" t="s">
         <v>269</v>
       </c>
-      <c r="I95" t="s">
+      <c r="J95" t="s">
         <v>270</v>
-      </c>
-      <c r="J95" t="s">
-        <v>271</v>
       </c>
       <c r="K95" t="s">
         <v>11</v>
@@ -29456,13 +29460,13 @@
         <v>11</v>
       </c>
       <c r="H96" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I96" t="s">
         <v>67</v>
       </c>
       <c r="J96" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K96" t="s">
         <v>11</v>
@@ -29509,13 +29513,13 @@
         <v>151</v>
       </c>
       <c r="H97" t="s">
+        <v>273</v>
+      </c>
+      <c r="I97" t="s">
+        <v>236</v>
+      </c>
+      <c r="J97" t="s">
         <v>274</v>
-      </c>
-      <c r="I97" t="s">
-        <v>237</v>
-      </c>
-      <c r="J97" t="s">
-        <v>275</v>
       </c>
       <c r="K97" t="s">
         <v>11</v>
@@ -29562,13 +29566,13 @@
         <v>139</v>
       </c>
       <c r="H98" t="s">
+        <v>275</v>
+      </c>
+      <c r="I98" t="s">
         <v>276</v>
       </c>
-      <c r="I98" t="s">
+      <c r="J98" t="s">
         <v>277</v>
-      </c>
-      <c r="J98" t="s">
-        <v>278</v>
       </c>
       <c r="K98" t="s">
         <v>11</v>
@@ -29615,13 +29619,13 @@
         <v>148</v>
       </c>
       <c r="H99" t="s">
+        <v>278</v>
+      </c>
+      <c r="I99" t="s">
         <v>279</v>
       </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>280</v>
-      </c>
-      <c r="J99" t="s">
-        <v>281</v>
       </c>
       <c r="K99" t="s">
         <v>11</v>
@@ -29668,13 +29672,13 @@
         <v>91</v>
       </c>
       <c r="H100" t="s">
+        <v>281</v>
+      </c>
+      <c r="I100" t="s">
         <v>282</v>
       </c>
-      <c r="I100" t="s">
+      <c r="J100" t="s">
         <v>283</v>
-      </c>
-      <c r="J100" t="s">
-        <v>284</v>
       </c>
       <c r="K100" t="s">
         <v>11</v>
@@ -29721,13 +29725,13 @@
         <v>122</v>
       </c>
       <c r="H101" t="s">
+        <v>284</v>
+      </c>
+      <c r="I101" t="s">
         <v>285</v>
       </c>
-      <c r="I101" t="s">
+      <c r="J101" t="s">
         <v>286</v>
-      </c>
-      <c r="J101" t="s">
-        <v>287</v>
       </c>
       <c r="K101" t="s">
         <v>11</v>
@@ -29774,13 +29778,13 @@
         <v>115</v>
       </c>
       <c r="H102" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I102" t="s">
         <v>67</v>
       </c>
       <c r="J102" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K102" t="s">
         <v>11</v>
@@ -29827,13 +29831,13 @@
         <v>110</v>
       </c>
       <c r="H103" t="s">
+        <v>289</v>
+      </c>
+      <c r="I103" t="s">
+        <v>282</v>
+      </c>
+      <c r="J103" t="s">
         <v>290</v>
-      </c>
-      <c r="I103" t="s">
-        <v>283</v>
-      </c>
-      <c r="J103" t="s">
-        <v>291</v>
       </c>
       <c r="K103" t="s">
         <v>11</v>
@@ -29880,13 +29884,13 @@
         <v>116</v>
       </c>
       <c r="H104" t="s">
+        <v>291</v>
+      </c>
+      <c r="I104" t="s">
+        <v>47</v>
+      </c>
+      <c r="J104" t="s">
         <v>292</v>
-      </c>
-      <c r="I104" t="s">
-        <v>227</v>
-      </c>
-      <c r="J104" t="s">
-        <v>293</v>
       </c>
       <c r="K104" t="s">
         <v>11</v>
@@ -29933,13 +29937,13 @@
         <v>98</v>
       </c>
       <c r="H105" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I105" t="s">
         <v>114</v>
       </c>
       <c r="J105" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K105" t="s">
         <v>11</v>
@@ -29986,13 +29990,13 @@
         <v>119</v>
       </c>
       <c r="H106" t="s">
+        <v>295</v>
+      </c>
+      <c r="I106" t="s">
+        <v>47</v>
+      </c>
+      <c r="J106" t="s">
         <v>296</v>
-      </c>
-      <c r="I106" t="s">
-        <v>227</v>
-      </c>
-      <c r="J106" t="s">
-        <v>297</v>
       </c>
       <c r="K106" t="s">
         <v>11</v>
@@ -30039,13 +30043,13 @@
         <v>11</v>
       </c>
       <c r="H107" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I107" t="s">
         <v>67</v>
       </c>
       <c r="J107" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K107" t="s">
         <v>11</v>
@@ -30092,13 +30096,13 @@
         <v>86</v>
       </c>
       <c r="H108" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I108" t="s">
         <v>158</v>
       </c>
       <c r="J108" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K108" t="s">
         <v>11</v>
@@ -30145,13 +30149,13 @@
         <v>129</v>
       </c>
       <c r="H109" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I109" t="s">
         <v>67</v>
       </c>
       <c r="J109" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K109" t="s">
         <v>11</v>
@@ -30198,13 +30202,13 @@
         <v>11</v>
       </c>
       <c r="H110" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I110" t="s">
         <v>47</v>
       </c>
       <c r="J110" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K110" t="s">
         <v>11</v>
@@ -30251,13 +30255,13 @@
         <v>142</v>
       </c>
       <c r="H111" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I111" t="s">
         <v>47</v>
       </c>
       <c r="J111" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K111" t="s">
         <v>11</v>
@@ -30304,13 +30308,13 @@
         <v>11</v>
       </c>
       <c r="H112" t="s">
+        <v>307</v>
+      </c>
+      <c r="I112" t="s">
         <v>308</v>
       </c>
-      <c r="I112" t="s">
+      <c r="J112" t="s">
         <v>309</v>
-      </c>
-      <c r="J112" t="s">
-        <v>310</v>
       </c>
       <c r="K112" t="s">
         <v>11</v>
@@ -30363,7 +30367,7 @@
         <v>67</v>
       </c>
       <c r="J113" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K113" t="s">
         <v>11</v>
@@ -30410,13 +30414,13 @@
         <v>152</v>
       </c>
       <c r="H114" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I114" t="s">
         <v>114</v>
       </c>
       <c r="J114" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K114" t="s">
         <v>11</v>
@@ -30463,13 +30467,13 @@
         <v>108</v>
       </c>
       <c r="H115" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I115" t="s">
         <v>114</v>
       </c>
       <c r="J115" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K115" t="s">
         <v>11</v>
@@ -30516,13 +30520,13 @@
         <v>94</v>
       </c>
       <c r="H116" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I116" t="s">
         <v>114</v>
       </c>
       <c r="J116" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K116" t="s">
         <v>11</v>
@@ -30569,13 +30573,13 @@
         <v>89</v>
       </c>
       <c r="H117" t="s">
+        <v>317</v>
+      </c>
+      <c r="I117" t="s">
         <v>318</v>
       </c>
-      <c r="I117" t="s">
+      <c r="J117" t="s">
         <v>319</v>
-      </c>
-      <c r="J117" t="s">
-        <v>320</v>
       </c>
       <c r="K117" t="s">
         <v>11</v>
@@ -30625,10 +30629,10 @@
         <v>33</v>
       </c>
       <c r="I118" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J118" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K118" t="s">
         <v>11</v>
@@ -30678,10 +30682,10 @@
         <v>33</v>
       </c>
       <c r="I119" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J119" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K119" t="s">
         <v>11</v>
@@ -30728,13 +30732,13 @@
         <v>74</v>
       </c>
       <c r="H120" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I120" t="s">
         <v>72</v>
       </c>
       <c r="J120" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K120" t="s">
         <v>11</v>
@@ -30781,10 +30785,10 @@
         <v>135</v>
       </c>
       <c r="H121" t="s">
+        <v>322</v>
+      </c>
+      <c r="I121" t="s">
         <v>323</v>
-      </c>
-      <c r="I121" t="s">
-        <v>230</v>
       </c>
       <c r="J121" t="s">
         <v>324</v>
@@ -52469,7 +52473,7 @@
         <v>360</v>
       </c>
       <c r="M386" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N386" t="b">
         <v>1</v>
@@ -52669,7 +52673,7 @@
         <v>360</v>
       </c>
       <c r="M390" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N390" t="b">
         <v>1</v>
@@ -52919,7 +52923,7 @@
         <v>360</v>
       </c>
       <c r="M395" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N395" t="b">
         <v>1</v>
@@ -53119,7 +53123,7 @@
         <v>360</v>
       </c>
       <c r="M399" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N399" t="b">
         <v>1</v>
@@ -53269,7 +53273,7 @@
         <v>360</v>
       </c>
       <c r="M402" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N402" t="b">
         <v>1</v>
@@ -53469,7 +53473,7 @@
         <v>360</v>
       </c>
       <c r="M406" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N406" t="b">
         <v>1</v>
@@ -53619,7 +53623,7 @@
         <v>360</v>
       </c>
       <c r="M409" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N409" t="b">
         <v>1</v>
@@ -53869,7 +53873,7 @@
         <v>360</v>
       </c>
       <c r="M414" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N414" t="b">
         <v>1</v>
@@ -54069,7 +54073,7 @@
         <v>360</v>
       </c>
       <c r="M418" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N418" t="b">
         <v>1</v>
@@ -54269,7 +54273,7 @@
         <v>360</v>
       </c>
       <c r="M422" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N422" t="b">
         <v>1</v>
@@ -54519,7 +54523,7 @@
         <v>360</v>
       </c>
       <c r="M427" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N427" t="b">
         <v>1</v>
@@ -54719,7 +54723,7 @@
         <v>360</v>
       </c>
       <c r="M431" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N431" t="b">
         <v>1</v>
@@ -54969,7 +54973,7 @@
         <v>360</v>
       </c>
       <c r="M436" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N436" t="b">
         <v>1</v>
@@ -55169,7 +55173,7 @@
         <v>360</v>
       </c>
       <c r="M440" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N440" t="b">
         <v>1</v>
@@ -55369,7 +55373,7 @@
         <v>360</v>
       </c>
       <c r="M444" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N444" t="b">
         <v>1</v>
@@ -55619,7 +55623,7 @@
         <v>360</v>
       </c>
       <c r="M449" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N449" t="b">
         <v>1</v>
@@ -55919,7 +55923,7 @@
         <v>360</v>
       </c>
       <c r="M455" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N455" t="b">
         <v>1</v>
@@ -56119,7 +56123,7 @@
         <v>360</v>
       </c>
       <c r="M459" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N459" t="b">
         <v>1</v>
@@ -56269,7 +56273,7 @@
         <v>360</v>
       </c>
       <c r="M462" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N462" t="b">
         <v>1</v>
@@ -56469,7 +56473,7 @@
         <v>360</v>
       </c>
       <c r="M466" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N466" t="b">
         <v>1</v>
@@ -56669,7 +56673,7 @@
         <v>360</v>
       </c>
       <c r="M470" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N470" t="b">
         <v>1</v>
@@ -57119,7 +57123,7 @@
         <v>360</v>
       </c>
       <c r="M479" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N479" t="b">
         <v>1</v>
@@ -57319,7 +57323,7 @@
         <v>360</v>
       </c>
       <c r="M483" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N483" t="b">
         <v>1</v>
@@ -57519,7 +57523,7 @@
         <v>360</v>
       </c>
       <c r="M487" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N487" t="b">
         <v>1</v>
@@ -57669,7 +57673,7 @@
         <v>360</v>
       </c>
       <c r="M490" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N490" t="b">
         <v>1</v>
@@ -57869,7 +57873,7 @@
         <v>360</v>
       </c>
       <c r="M494" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N494" t="b">
         <v>1</v>
@@ -58069,7 +58073,7 @@
         <v>360</v>
       </c>
       <c r="M498" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N498" t="b">
         <v>1</v>
@@ -58219,7 +58223,7 @@
         <v>360</v>
       </c>
       <c r="M501" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N501" t="b">
         <v>1</v>
@@ -58419,7 +58423,7 @@
         <v>360</v>
       </c>
       <c r="M505" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N505" t="b">
         <v>1</v>
@@ -58669,7 +58673,7 @@
         <v>360</v>
       </c>
       <c r="M510" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N510" t="b">
         <v>1</v>
@@ -58869,7 +58873,7 @@
         <v>360</v>
       </c>
       <c r="M514" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N514" t="b">
         <v>1</v>
@@ -59019,7 +59023,7 @@
         <v>360</v>
       </c>
       <c r="M517" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N517" t="b">
         <v>1</v>
@@ -59269,7 +59273,7 @@
         <v>360</v>
       </c>
       <c r="M522" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N522" t="b">
         <v>1</v>
@@ -59419,7 +59423,7 @@
         <v>360</v>
       </c>
       <c r="M525" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N525" t="b">
         <v>1</v>
@@ -59669,7 +59673,7 @@
         <v>360</v>
       </c>
       <c r="M530" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N530" t="b">
         <v>1</v>
@@ -59969,7 +59973,7 @@
         <v>360</v>
       </c>
       <c r="M536" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N536" t="b">
         <v>1</v>
@@ -60119,7 +60123,7 @@
         <v>360</v>
       </c>
       <c r="M539" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N539" t="b">
         <v>1</v>
@@ -60269,7 +60273,7 @@
         <v>360</v>
       </c>
       <c r="M542" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N542" t="b">
         <v>1</v>
@@ -60419,7 +60423,7 @@
         <v>360</v>
       </c>
       <c r="M545" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N545" t="b">
         <v>1</v>
@@ -60619,7 +60623,7 @@
         <v>360</v>
       </c>
       <c r="M549" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N549" t="b">
         <v>1</v>
@@ -60769,7 +60773,7 @@
         <v>360</v>
       </c>
       <c r="M552" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N552" t="b">
         <v>1</v>
@@ -60969,7 +60973,7 @@
         <v>360</v>
       </c>
       <c r="M556" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N556" t="b">
         <v>1</v>
@@ -61169,7 +61173,7 @@
         <v>360</v>
       </c>
       <c r="M560" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N560" t="b">
         <v>1</v>
@@ -61369,7 +61373,7 @@
         <v>360</v>
       </c>
       <c r="M564" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N564" t="b">
         <v>1</v>
